--- a/artfynd/A 11156-2024 artfynd.xlsx
+++ b/artfynd/A 11156-2024 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>121344499</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11156-2024 artfynd.xlsx
+++ b/artfynd/A 11156-2024 artfynd.xlsx
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Amanda Tas</t>
+          <t>Amanda Tas, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 11156-2024 artfynd.xlsx
+++ b/artfynd/A 11156-2024 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>121344499</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Tas, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Amanda Tas</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 11156-2024 artfynd.xlsx
+++ b/artfynd/A 11156-2024 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>121344499</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Amanda Tas</t>
+          <t>Amanda Tas, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 11156-2024 artfynd.xlsx
+++ b/artfynd/A 11156-2024 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>121344499</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Tas, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Amanda Tas</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 11156-2024 artfynd.xlsx
+++ b/artfynd/A 11156-2024 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>121344499</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11156-2024 artfynd.xlsx
+++ b/artfynd/A 11156-2024 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>121344499</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11156-2024 artfynd.xlsx
+++ b/artfynd/A 11156-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115663652</v>
+        <v>115663631</v>
       </c>
       <c r="B2" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345984</v>
+        <v>346086</v>
       </c>
       <c r="R2" t="n">
-        <v>6606531</v>
+        <v>6606494</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas, Roger Adolfsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,12 +775,7 @@
         <v>115663666</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115663650</v>
+        <v>115663674</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346086</v>
+        <v>346119</v>
       </c>
       <c r="R4" t="n">
-        <v>6606504</v>
+        <v>6606447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-04-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 exemplar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,50 +976,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115663631</v>
+        <v>121344499</v>
       </c>
       <c r="B5" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Mörtnäs, Vrm</t>
+          <t>Rundmyren, NO om, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346086</v>
+        <v>346162</v>
       </c>
       <c r="R5" t="n">
-        <v>6606494</v>
+        <v>6606426</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,6 +1048,11 @@
           <t>Karlanda</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>S-Årj-0403</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -1062,6 +1061,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-04-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 dellokaler. Ca 70 exemplar vid angiven koordinat samt 10 ex vid RT90: 6610605 - 1300578.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,49 +1080,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Roger Adolfsson, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115663674</v>
+        <v>115663650</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346119</v>
+        <v>346086</v>
       </c>
       <c r="R6" t="n">
-        <v>6606447</v>
+        <v>6606504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1167,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-04-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>10 exemplar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,59 +1193,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344499</v>
+        <v>115663652</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rundmyren, NO om, Vrm</t>
+          <t>Östra Mörtnäs, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346162</v>
+        <v>345984</v>
       </c>
       <c r="R7" t="n">
-        <v>6606426</v>
+        <v>6606531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,11 +1256,6 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>S-Årj-0403</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -1285,11 +1264,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-04-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 dellokaler. Ca 70 exemplar vid angiven koordinat samt 10 ex vid RT90: 6610605 - 1300578.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,19 +1278,15 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Amanda Tas, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
